--- a/development/Orchestration/assets/Orchestration-1.2.0-XFWB-5.0.0-mapping.xlsx
+++ b/development/Orchestration/assets/Orchestration-1.2.0-XFWB-5.0.0-mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iataonline-my.sharepoint.com/personal/lambertc_iata_org/Documents/ONE Record/31 CXML mapping/Ochestration 1.2.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{7A6CA4D8-11C1-4AD9-AA64-9849092C22BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBD8D004-470F-4FEC-A62C-DFF41594BE69}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="13_ncr:1_{7A6CA4D8-11C1-4AD9-AA64-9849092C22BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF2279D3-830A-43F5-9B0D-B1758ED41072}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-30" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{FDB6F52B-EA41-4419-BE36-DF3522468846}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{FDB6F52B-EA41-4419-BE36-DF3522468846}"/>
   </bookViews>
   <sheets>
     <sheet name="Versioning" sheetId="4" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4524" uniqueCount="895">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4518" uniqueCount="899">
   <si>
     <t>Date</t>
   </si>
@@ -2560,12 +2560,6 @@
     <t>prefix+number</t>
   </si>
   <si>
-    <t>ExternalReference#documentType = FF Assigned ID</t>
-  </si>
-  <si>
-    <t>ExternalReference#documentType = Associated Reference ID</t>
-  </si>
-  <si>
     <t>Mapping remark</t>
   </si>
   <si>
@@ -2669,9 +2663,6 @@
   </si>
   <si>
     <t>Party#partyRole must be code-lists:CNE</t>
-  </si>
-  <si>
-    <t>Party#partyRole must be code-lists:FFW</t>
   </si>
   <si>
     <t>OtherIdentifier#otherIdentifierType = "Forwarder Internal ID"</t>
@@ -2730,6 +2721,27 @@
   </si>
   <si>
     <t>UnitComposition#slac</t>
+  </si>
+  <si>
+    <t>Waybill#otherChargeIndicator</t>
+  </si>
+  <si>
+    <t>Party#partyRole must be code-lists:AGT</t>
+  </si>
+  <si>
+    <t>Waybill#valuationCharge</t>
+  </si>
+  <si>
+    <t>Waybill#agentReference</t>
+  </si>
+  <si>
+    <t>Waybill#otherIdentifiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OtherIdentifier#otherIdentifierType = "Other Party Reference" </t>
+  </si>
+  <si>
+    <t>Please refer to the part on the documentation about handling of goodsDescription to identify if mapping is done to Shipment or Pieces</t>
   </si>
 </sst>
 </file>
@@ -2982,21 +2994,21 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3397,31 +3409,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
       <c r="J1" s="10" t="s">
         <v>12</v>
       </c>
       <c r="L1" s="5"/>
     </row>
     <row r="2" spans="1:25" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="6" t="s">
         <v>14</v>
       </c>
@@ -3443,18 +3455,18 @@
       <c r="M2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="55" t="s">
+      <c r="N2" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="56"/>
-      <c r="V2" s="56"/>
-      <c r="W2" s="56"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="58"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="58"/>
+      <c r="S2" s="58"/>
+      <c r="T2" s="58"/>
+      <c r="U2" s="58"/>
+      <c r="V2" s="58"/>
+      <c r="W2" s="58"/>
       <c r="X2" s="7" t="s">
         <v>21</v>
       </c>
@@ -12755,31 +12767,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
       <c r="J1" s="10" t="s">
         <v>12</v>
       </c>
       <c r="W1" s="5"/>
     </row>
     <row r="2" spans="1:23" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="6" t="s">
         <v>14</v>
       </c>
@@ -12794,22 +12806,22 @@
       </c>
       <c r="K2" s="40"/>
       <c r="L2" s="38" t="s">
-        <v>840</v>
-      </c>
-      <c r="M2" s="57" t="s">
+        <v>838</v>
+      </c>
+      <c r="M2" s="55" t="s">
         <v>821</v>
       </c>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
       <c r="W2" s="7" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
@@ -13435,17 +13447,9 @@
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="41"/>
-      <c r="L39" t="s">
-        <v>838</v>
-      </c>
+      <c r="L39"/>
       <c r="M39" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="N39" t="s">
-        <v>116</v>
-      </c>
-      <c r="O39" t="s">
-        <v>117</v>
+        <v>895</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
@@ -13464,16 +13468,13 @@
       <c r="J40" s="3"/>
       <c r="K40" s="41"/>
       <c r="L40" t="s">
-        <v>839</v>
+        <v>897</v>
       </c>
       <c r="M40" s="28" t="s">
-        <v>115</v>
+        <v>896</v>
       </c>
       <c r="N40" t="s">
-        <v>116</v>
-      </c>
-      <c r="O40" t="s">
-        <v>117</v>
+        <v>866</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.25">
@@ -13494,7 +13495,7 @@
       </c>
       <c r="K41" s="41"/>
       <c r="L41" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="M41" s="28"/>
       <c r="W41" t="s">
@@ -13541,7 +13542,7 @@
       </c>
       <c r="K43" s="41"/>
       <c r="L43" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="M43" s="28"/>
       <c r="W43" t="s">
@@ -13588,7 +13589,7 @@
       </c>
       <c r="K45" s="41"/>
       <c r="L45" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="M45" s="28"/>
       <c r="W45" t="s">
@@ -13669,7 +13670,7 @@
       <c r="K48" s="41"/>
       <c r="L48"/>
       <c r="M48" s="28" t="s">
-        <v>155</v>
+        <v>892</v>
       </c>
       <c r="W48" t="s">
         <v>154</v>
@@ -13693,7 +13694,7 @@
       </c>
       <c r="K49" s="41"/>
       <c r="L49" s="52" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="M49" s="28" t="s">
         <v>140</v>
@@ -13718,7 +13719,7 @@
       <c r="J50" s="3"/>
       <c r="K50" s="41"/>
       <c r="L50" s="52" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="M50" s="28" t="s">
         <v>140</v>
@@ -13775,7 +13776,7 @@
       <c r="J52" s="3"/>
       <c r="K52" s="41"/>
       <c r="L52" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="M52" s="28" t="s">
         <v>140</v>
@@ -13805,7 +13806,7 @@
       </c>
       <c r="K53" s="41"/>
       <c r="L53" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="M53" s="28" t="s">
         <v>140</v>
@@ -13856,7 +13857,7 @@
       </c>
       <c r="K55" s="43"/>
       <c r="L55" s="46" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="M55" s="49" t="s">
         <v>140</v>
@@ -13893,7 +13894,7 @@
       <c r="J56" s="15"/>
       <c r="K56" s="43"/>
       <c r="L56" s="44" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="M56" s="49" t="s">
         <v>140</v>
@@ -13908,7 +13909,7 @@
         <v>198</v>
       </c>
       <c r="Q56" s="44" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="R56" s="44"/>
       <c r="S56" s="44"/>
@@ -13934,7 +13935,7 @@
       <c r="J57" s="15"/>
       <c r="K57" s="43"/>
       <c r="L57" s="44" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="M57" s="49" t="s">
         <v>140</v>
@@ -13949,7 +13950,7 @@
         <v>198</v>
       </c>
       <c r="Q57" s="44" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="R57" s="44"/>
       <c r="S57" s="44"/>
@@ -14012,7 +14013,7 @@
       <c r="J59" s="15"/>
       <c r="K59" s="43"/>
       <c r="L59" s="46" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="M59" s="49" t="s">
         <v>140</v>
@@ -14021,13 +14022,13 @@
         <v>191</v>
       </c>
       <c r="O59" s="44" t="s">
+        <v>863</v>
+      </c>
+      <c r="P59" s="44" t="s">
+        <v>864</v>
+      </c>
+      <c r="Q59" s="44" t="s">
         <v>865</v>
-      </c>
-      <c r="P59" s="44" t="s">
-        <v>866</v>
-      </c>
-      <c r="Q59" s="44" t="s">
-        <v>867</v>
       </c>
       <c r="R59" s="44"/>
       <c r="S59" s="44"/>
@@ -14177,7 +14178,7 @@
         <v>214</v>
       </c>
       <c r="R63" s="44" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="S63" s="44"/>
       <c r="T63" s="50"/>
@@ -14202,7 +14203,7 @@
       <c r="J64" s="15"/>
       <c r="K64" s="43"/>
       <c r="L64" s="52" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="M64" s="49" t="s">
         <v>140</v>
@@ -14245,7 +14246,7 @@
       <c r="J65" s="15"/>
       <c r="K65" s="43"/>
       <c r="L65" s="44" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="M65" s="49"/>
       <c r="N65" s="44"/>
@@ -14276,7 +14277,7 @@
       <c r="J66" s="15"/>
       <c r="K66" s="43"/>
       <c r="L66" s="52" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="M66" s="49" t="s">
         <v>140</v>
@@ -14586,7 +14587,7 @@
       <c r="J75" s="15"/>
       <c r="K75" s="43"/>
       <c r="L75" s="52" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="M75" s="49" t="s">
         <v>140</v>
@@ -14659,7 +14660,7 @@
       <c r="J78" s="15"/>
       <c r="K78" s="43"/>
       <c r="L78" s="52" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="M78" s="49" t="s">
         <v>140</v>
@@ -14733,7 +14734,7 @@
       <c r="J81" s="15"/>
       <c r="K81" s="43"/>
       <c r="L81" s="52" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="M81" s="49" t="s">
         <v>140</v>
@@ -14807,7 +14808,7 @@
       <c r="J84" s="15"/>
       <c r="K84" s="43"/>
       <c r="L84" s="52" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="M84" s="49" t="s">
         <v>140</v>
@@ -14912,7 +14913,7 @@
       </c>
       <c r="K88" s="43"/>
       <c r="L88" s="46" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="M88" s="49" t="s">
         <v>140</v>
@@ -14949,7 +14950,7 @@
       <c r="J89" s="15"/>
       <c r="K89" s="43"/>
       <c r="L89" s="44" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="M89" s="49" t="s">
         <v>140</v>
@@ -14988,7 +14989,7 @@
       <c r="J90" s="15"/>
       <c r="K90" s="43"/>
       <c r="L90" s="44" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="M90" s="49" t="s">
         <v>140</v>
@@ -15064,7 +15065,7 @@
       <c r="J92" s="15"/>
       <c r="K92" s="43"/>
       <c r="L92" s="46" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="M92" s="49" t="s">
         <v>140</v>
@@ -15073,13 +15074,13 @@
         <v>191</v>
       </c>
       <c r="O92" s="44" t="s">
+        <v>863</v>
+      </c>
+      <c r="P92" s="44" t="s">
+        <v>864</v>
+      </c>
+      <c r="Q92" s="44" t="s">
         <v>865</v>
-      </c>
-      <c r="P92" s="44" t="s">
-        <v>866</v>
-      </c>
-      <c r="Q92" s="44" t="s">
-        <v>867</v>
       </c>
       <c r="R92" s="44"/>
       <c r="S92" s="44"/>
@@ -15229,7 +15230,7 @@
         <v>214</v>
       </c>
       <c r="R96" s="44" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="S96" s="44"/>
       <c r="T96" s="50"/>
@@ -15254,7 +15255,7 @@
       <c r="J97" s="15"/>
       <c r="K97" s="43"/>
       <c r="L97" s="52" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="M97" s="49" t="s">
         <v>140</v>
@@ -15297,7 +15298,7 @@
       <c r="J98" s="15"/>
       <c r="K98" s="43"/>
       <c r="L98" s="44" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="M98" s="49"/>
       <c r="N98" s="44"/>
@@ -15328,7 +15329,7 @@
       <c r="J99" s="15"/>
       <c r="K99" s="43"/>
       <c r="L99" s="52" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="M99" s="49" t="s">
         <v>140</v>
@@ -15638,7 +15639,7 @@
       <c r="J108" s="15"/>
       <c r="K108" s="43"/>
       <c r="L108" s="52" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="M108" s="49" t="s">
         <v>140</v>
@@ -15711,7 +15712,7 @@
       <c r="J111" s="15"/>
       <c r="K111" s="43"/>
       <c r="L111" s="52" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="M111" s="49" t="s">
         <v>140</v>
@@ -15785,7 +15786,7 @@
       <c r="J114" s="15"/>
       <c r="K114" s="43"/>
       <c r="L114" s="52" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="M114" s="49" t="s">
         <v>140</v>
@@ -15859,7 +15860,7 @@
       <c r="J117" s="15"/>
       <c r="K117" s="43"/>
       <c r="L117" s="52" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="M117" s="49" t="s">
         <v>140</v>
@@ -15964,7 +15965,7 @@
       </c>
       <c r="K121" s="43"/>
       <c r="L121" s="46" t="s">
-        <v>875</v>
+        <v>893</v>
       </c>
       <c r="M121" s="49" t="s">
         <v>140</v>
@@ -16001,7 +16002,7 @@
       <c r="J122" s="14"/>
       <c r="K122" s="43"/>
       <c r="L122" s="44" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="M122" s="49" t="s">
         <v>140</v>
@@ -16040,7 +16041,7 @@
       <c r="J123" s="14"/>
       <c r="K123" s="43"/>
       <c r="L123" s="44" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="M123" s="49" t="s">
         <v>140</v>
@@ -16116,7 +16117,7 @@
       <c r="J125" s="14"/>
       <c r="K125" s="43"/>
       <c r="L125" s="46" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="M125" s="49" t="s">
         <v>140</v>
@@ -16125,13 +16126,13 @@
         <v>191</v>
       </c>
       <c r="O125" s="44" t="s">
+        <v>863</v>
+      </c>
+      <c r="P125" s="44" t="s">
+        <v>864</v>
+      </c>
+      <c r="Q125" s="44" t="s">
         <v>865</v>
-      </c>
-      <c r="P125" s="44" t="s">
-        <v>866</v>
-      </c>
-      <c r="Q125" s="44" t="s">
-        <v>867</v>
       </c>
       <c r="R125" s="44"/>
       <c r="S125" s="44"/>
@@ -16318,7 +16319,7 @@
         <v>214</v>
       </c>
       <c r="R130" s="44" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="S130" s="44"/>
       <c r="T130" s="50"/>
@@ -16343,7 +16344,7 @@
       <c r="J131" s="14"/>
       <c r="K131" s="43"/>
       <c r="L131" s="52" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="M131" s="49" t="s">
         <v>140</v>
@@ -16386,7 +16387,7 @@
       <c r="J132" s="14"/>
       <c r="K132" s="43"/>
       <c r="L132" s="44" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="M132" s="49"/>
       <c r="N132" s="44"/>
@@ -16417,7 +16418,7 @@
       <c r="J133" s="14"/>
       <c r="K133" s="43"/>
       <c r="L133" s="52" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="M133" s="49" t="s">
         <v>140</v>
@@ -16812,7 +16813,7 @@
       <c r="J145" s="14"/>
       <c r="K145" s="43"/>
       <c r="L145" s="52" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="M145" s="49" t="s">
         <v>140</v>
@@ -16891,7 +16892,7 @@
       <c r="J148" s="14"/>
       <c r="K148" s="43"/>
       <c r="L148" s="52" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="M148" s="49" t="s">
         <v>140</v>
@@ -16971,7 +16972,7 @@
       <c r="J151" s="14"/>
       <c r="K151" s="43"/>
       <c r="L151" s="52" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="M151" s="49" t="s">
         <v>140</v>
@@ -17051,7 +17052,7 @@
       <c r="J154" s="14"/>
       <c r="K154" s="43"/>
       <c r="L154" s="52" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="M154" s="49" t="s">
         <v>140</v>
@@ -17299,7 +17300,7 @@
       <c r="J162" s="13"/>
       <c r="K162" s="43"/>
       <c r="L162" s="44" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="M162" s="49" t="s">
         <v>140</v>
@@ -17457,7 +17458,7 @@
         <v>214</v>
       </c>
       <c r="R167" s="44" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="S167" s="44"/>
       <c r="T167" s="50"/>
@@ -17480,7 +17481,7 @@
       <c r="J168" s="3"/>
       <c r="K168" s="43"/>
       <c r="L168" s="52" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="M168" s="49" t="s">
         <v>140</v>
@@ -17521,7 +17522,7 @@
       <c r="J169" s="3"/>
       <c r="K169" s="43"/>
       <c r="L169" s="44" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="M169" s="49"/>
       <c r="N169" s="44"/>
@@ -17550,7 +17551,7 @@
       <c r="J170" s="3"/>
       <c r="K170" s="43"/>
       <c r="L170" s="52" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="M170" s="49" t="s">
         <v>140</v>
@@ -17958,7 +17959,7 @@
       <c r="J184" s="3"/>
       <c r="K184" s="43"/>
       <c r="L184" s="52" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="M184" s="49" t="s">
         <v>140</v>
@@ -18022,7 +18023,7 @@
       <c r="J187" s="3"/>
       <c r="K187" s="43"/>
       <c r="L187" s="52" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="M187" s="49" t="s">
         <v>140</v>
@@ -18088,7 +18089,7 @@
       <c r="J190" s="3"/>
       <c r="K190" s="43"/>
       <c r="L190" s="52" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="M190" s="49" t="s">
         <v>140</v>
@@ -18153,7 +18154,7 @@
       <c r="J193" s="3"/>
       <c r="K193" s="43"/>
       <c r="L193" s="52" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="M193" s="49" t="s">
         <v>140</v>
@@ -18387,7 +18388,7 @@
       <c r="J206" s="3"/>
       <c r="K206" s="41"/>
       <c r="L206" s="45" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="M206" s="28" t="s">
         <v>182</v>
@@ -18418,7 +18419,7 @@
       <c r="J207" s="3"/>
       <c r="K207" s="41"/>
       <c r="L207" s="45" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="M207" s="28" t="s">
         <v>182</v>
@@ -18507,7 +18508,7 @@
         <v>819</v>
       </c>
       <c r="O210" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="211" spans="3:19" x14ac:dyDescent="0.25">
@@ -18543,7 +18544,7 @@
       </c>
       <c r="K212" s="41"/>
       <c r="L212" s="46" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="M212" s="28" t="s">
         <v>182</v>
@@ -18555,7 +18556,7 @@
         <v>820</v>
       </c>
       <c r="P212" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="Q212" t="s">
         <v>192</v>
@@ -18590,7 +18591,7 @@
       <c r="J214" s="3"/>
       <c r="K214" s="41"/>
       <c r="L214" s="45" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="M214" s="28" t="s">
         <v>182</v>
@@ -18640,9 +18641,6 @@
       </c>
       <c r="Q215" t="s">
         <v>406</v>
-      </c>
-      <c r="R215" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="216" spans="3:19" x14ac:dyDescent="0.25">
@@ -18791,7 +18789,7 @@
       <c r="J222" s="3"/>
       <c r="K222" s="41"/>
       <c r="L222" s="45" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="M222" s="28" t="s">
         <v>182</v>
@@ -18841,9 +18839,6 @@
       </c>
       <c r="Q223" t="s">
         <v>406</v>
-      </c>
-      <c r="R223" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="224" spans="3:19" x14ac:dyDescent="0.25">
@@ -19491,7 +19486,7 @@
       <c r="J255" s="3"/>
       <c r="K255" s="42"/>
       <c r="L255" s="22" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="M255" s="28" t="s">
         <v>140</v>
@@ -19500,7 +19495,7 @@
         <v>485</v>
       </c>
       <c r="O255" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="256" spans="2:23" x14ac:dyDescent="0.25">
@@ -19609,7 +19604,7 @@
       </c>
       <c r="K259" s="41"/>
       <c r="L259" s="52" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="M259" s="28" t="s">
         <v>140</v>
@@ -19827,16 +19822,16 @@
       </c>
       <c r="K271" s="42"/>
       <c r="L271" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="M271" s="28" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="N271" t="s">
         <v>724</v>
       </c>
       <c r="O271" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
     </row>
     <row r="272" spans="2:15" x14ac:dyDescent="0.25">
@@ -20382,10 +20377,10 @@
       </c>
       <c r="K298" s="42"/>
       <c r="L298" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="M298" s="28" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="N298" t="s">
         <v>724</v>
@@ -20410,10 +20405,10 @@
       <c r="J299" s="3"/>
       <c r="K299" s="42"/>
       <c r="L299" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="M299" s="28" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="300" spans="2:23" x14ac:dyDescent="0.25">
@@ -20509,7 +20504,7 @@
       </c>
       <c r="K303" s="41"/>
       <c r="L303" s="52" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="M303" s="28" t="s">
         <v>614</v>
@@ -20536,7 +20531,7 @@
       </c>
       <c r="K304" s="41"/>
       <c r="L304" s="52" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="M304" s="28" t="s">
         <v>614</v>
@@ -20621,7 +20616,7 @@
         <v>614</v>
       </c>
       <c r="N307" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
     </row>
     <row r="308" spans="4:23" x14ac:dyDescent="0.25">
@@ -20679,7 +20674,9 @@
         <v>618</v>
       </c>
       <c r="K310" s="41"/>
-      <c r="L310"/>
+      <c r="L310" t="s">
+        <v>898</v>
+      </c>
       <c r="M310" s="28" t="s">
         <v>614</v>
       </c>
@@ -20737,7 +20734,7 @@
       </c>
       <c r="K313" s="41"/>
       <c r="L313" s="52" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="M313" s="28" t="s">
         <v>614</v>
@@ -20802,7 +20799,7 @@
         <v>614</v>
       </c>
       <c r="N316" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="O316" t="s">
         <v>814</v>
@@ -20824,13 +20821,13 @@
       <c r="J317" s="3"/>
       <c r="K317" s="41"/>
       <c r="L317" s="52" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="M317" s="28" t="s">
         <v>614</v>
       </c>
       <c r="N317" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="O317" t="s">
         <v>815</v>
@@ -20856,13 +20853,13 @@
         <v>614</v>
       </c>
       <c r="N318" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="O318" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="P318" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
     </row>
     <row r="319" spans="4:23" x14ac:dyDescent="0.25">
@@ -20887,7 +20884,7 @@
         <v>614</v>
       </c>
       <c r="N319" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="O319" t="s">
         <v>816</v>
@@ -20930,7 +20927,7 @@
         <v>614</v>
       </c>
       <c r="N321" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="O321" t="s">
         <v>817</v>
@@ -21018,7 +21015,7 @@
       <c r="J326" s="3"/>
       <c r="K326" s="41"/>
       <c r="L326" s="52" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="M326" s="28" t="s">
         <v>614</v>
@@ -21063,7 +21060,7 @@
       </c>
       <c r="K328" s="41"/>
       <c r="L328" s="52" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="M328" s="28" t="s">
         <v>614</v>
@@ -21099,7 +21096,7 @@
       </c>
       <c r="K329" s="41"/>
       <c r="L329" s="52" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="M329" s="28" t="s">
         <v>614</v>
@@ -21135,7 +21132,7 @@
       </c>
       <c r="K330" s="41"/>
       <c r="L330" s="52" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="M330" s="28" t="s">
         <v>614</v>
@@ -21265,7 +21262,7 @@
       </c>
       <c r="K336" s="41"/>
       <c r="L336" s="52" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="M336" s="28" t="s">
         <v>614</v>
@@ -21320,7 +21317,7 @@
       </c>
       <c r="K338" s="41"/>
       <c r="L338" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="M338" s="28"/>
       <c r="W338" s="12" t="s">
@@ -21630,7 +21627,7 @@
       </c>
       <c r="K355" s="42"/>
       <c r="L355" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="M355" s="28"/>
     </row>
@@ -21732,7 +21729,7 @@
       <c r="J360" s="48"/>
       <c r="K360" s="42"/>
       <c r="L360" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="M360" s="28"/>
       <c r="N360"/>
@@ -21763,7 +21760,7 @@
       </c>
       <c r="K361" s="42"/>
       <c r="L361" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="M361" s="28"/>
       <c r="W361" t="s">
@@ -21788,11 +21785,9 @@
       </c>
       <c r="K362" s="41"/>
       <c r="L362" t="s">
-        <v>126</v>
-      </c>
-      <c r="M362" s="28" t="s">
-        <v>126</v>
-      </c>
+        <v>894</v>
+      </c>
+      <c r="M362" s="28"/>
       <c r="O362" s="44"/>
       <c r="P362" s="44"/>
       <c r="Q362" s="44"/>
@@ -21847,7 +21842,7 @@
       </c>
       <c r="K364" s="42"/>
       <c r="L364" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="M364" s="28"/>
     </row>
@@ -21869,7 +21864,7 @@
       </c>
       <c r="K365" s="42"/>
       <c r="L365" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="M365" s="28"/>
     </row>
